--- a/products-storage/16-chto-v-smete-ne-oplatyat/63-reestr-zatrat-po-obektu.xlsx
+++ b/products-storage/16-chto-v-smete-ne-oplatyat/63-reestr-zatrat-po-obektu.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр затрат" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Как заполнять" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Реестр затрат" sheetId="1" state="visible" ns1:id="rId1"/>
+    <sheet name="Как заполнять" sheetId="2" state="visible" ns1:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Реестр затрат'!$A$1:$J$56</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Реестр затрат'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Как заполнять'!$A$1:$B$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Как заполнять'!$1:$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,8 +39,35 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF27333D"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF27333D"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+      <color rgb="FF27333D"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF687780"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -48,8 +80,33 @@
         <bgColor rgb="00366092"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27333D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF7EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F5F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F7F7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -63,11 +120,40 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="FFDEE4E7"/>
+      </left>
+      <right style="hair">
+        <color rgb="FFDEE4E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FFDEE4E7"/>
+      </bottom>
+    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -80,6 +166,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" pivotButton="0" quotePrefix="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,7 +562,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -461,1211 +580,1231 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Раздел</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Затрата</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Учтено в смете</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Позиция сметы №</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Чья зона</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ответственная сторона</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Чем подтверждено</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Оценка, ₽</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="H1" t="str" s="8">
+        <v>Не покрыто, ₽</v>
+      </c>
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>1. Площадка и временное</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>Бытовка, раздевалка, помещение для приёма пищи</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="D2" s="10" t="inlineStr"/>
+      <c r="E2" s="10" t="inlineStr"/>
+      <c r="F2" s="10" t="inlineStr"/>
+      <c r="G2" s="10" t="inlineStr"/>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="10" t="inlineStr"/>
+      <c r="J2" s="10" t="inlineStr"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>1. Площадка и временное</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>Склад и место хранения материалов</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="D3" s="10" t="inlineStr"/>
+      <c r="E3" s="10" t="inlineStr"/>
+      <c r="F3" s="10" t="inlineStr"/>
+      <c r="G3" s="10" t="inlineStr"/>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="10" t="inlineStr"/>
+      <c r="J3" s="10" t="inlineStr"/>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>1. Площадка и временное</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Ограждение зоны работ, знаки, ограничение доступа</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="D4" s="10" t="inlineStr"/>
+      <c r="E4" s="10" t="inlineStr"/>
+      <c r="F4" s="10" t="inlineStr"/>
+      <c r="G4" s="10" t="inlineStr"/>
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="10" t="inlineStr"/>
+      <c r="J4" s="10" t="inlineStr"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>1. Площадка и временное</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Освещение рабочих мест и подходов</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="D5" s="10" t="inlineStr"/>
+      <c r="E5" s="10" t="inlineStr"/>
+      <c r="F5" s="10" t="inlineStr"/>
+      <c r="G5" s="10" t="inlineStr"/>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="10" t="inlineStr"/>
+      <c r="J5" s="10" t="inlineStr"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>1. Площадка и временное</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Электроэнергия, вода, тепло на период работ</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="D6" s="10" t="inlineStr"/>
+      <c r="E6" s="10" t="inlineStr"/>
+      <c r="F6" s="10" t="inlineStr"/>
+      <c r="G6" s="10" t="inlineStr"/>
+      <c r="H6" s="10" t="n"/>
+      <c r="I6" s="10" t="inlineStr"/>
+      <c r="J6" s="10" t="inlineStr"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>1. Площадка и временное</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Охрана, пропускной режим, оформление пропусков</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="D7" s="10" t="inlineStr"/>
+      <c r="E7" s="10" t="inlineStr"/>
+      <c r="F7" s="10" t="inlineStr"/>
+      <c r="G7" s="10" t="inlineStr"/>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="10" t="inlineStr"/>
+      <c r="J7" s="10" t="inlineStr"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>1. Площадка и временное</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Демонтаж и вывоз временного после работ</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="D8" s="10" t="inlineStr"/>
+      <c r="E8" s="10" t="inlineStr"/>
+      <c r="F8" s="10" t="inlineStr"/>
+      <c r="G8" s="10" t="inlineStr"/>
+      <c r="H8" s="10" t="n"/>
+      <c r="I8" s="10" t="inlineStr"/>
+      <c r="J8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>2. Материалы и логистика</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Доставка материалов до объекта</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="D9" s="10" t="inlineStr"/>
+      <c r="E9" s="10" t="inlineStr"/>
+      <c r="F9" s="10" t="inlineStr"/>
+      <c r="G9" s="10" t="inlineStr"/>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="10" t="inlineStr"/>
+      <c r="J9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>2. Материалы и логистика</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Разгрузка на объекте</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="D10" s="10" t="inlineStr"/>
+      <c r="E10" s="10" t="inlineStr"/>
+      <c r="F10" s="10" t="inlineStr"/>
+      <c r="G10" s="10" t="inlineStr"/>
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="10" t="inlineStr"/>
+      <c r="J10" s="10" t="inlineStr"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>2. Материалы и логистика</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Перемещение по объекту и подъём на отметку</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="D11" s="10" t="inlineStr"/>
+      <c r="E11" s="10" t="inlineStr"/>
+      <c r="F11" s="10" t="inlineStr"/>
+      <c r="G11" s="10" t="inlineStr"/>
+      <c r="H11" s="10" t="n"/>
+      <c r="I11" s="10" t="inlineStr"/>
+      <c r="J11" s="10" t="inlineStr"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>2. Материалы и логистика</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Хранение на объекте</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="D12" s="10" t="inlineStr"/>
+      <c r="E12" s="10" t="inlineStr"/>
+      <c r="F12" s="10" t="inlineStr"/>
+      <c r="G12" s="10" t="inlineStr"/>
+      <c r="H12" s="10" t="n"/>
+      <c r="I12" s="10" t="inlineStr"/>
+      <c r="J12" s="10" t="inlineStr"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>2. Материалы и логистика</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Бой, порча, естественная убыль</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr"/>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="D13" s="10" t="inlineStr"/>
+      <c r="E13" s="10" t="inlineStr"/>
+      <c r="F13" s="10" t="inlineStr"/>
+      <c r="G13" s="10" t="inlineStr"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="10" t="inlineStr"/>
+      <c r="J13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>2. Материалы и логистика</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Тара и упаковка, её возврат или утилизация</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="D14" s="10" t="inlineStr"/>
+      <c r="E14" s="10" t="inlineStr"/>
+      <c r="F14" s="10" t="inlineStr"/>
+      <c r="G14" s="10" t="inlineStr"/>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="10" t="inlineStr"/>
+      <c r="J14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>2. Материалы и логистика</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Входной контроль и приёмка материалов</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="D15" s="10" t="inlineStr"/>
+      <c r="E15" s="10" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="10" t="n"/>
+      <c r="I15" s="10" t="inlineStr"/>
+      <c r="J15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>3. Люди</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Персонал</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Доставка работников к объекту</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="D16" s="10" t="inlineStr"/>
+      <c r="E16" s="10" t="inlineStr"/>
+      <c r="F16" s="10" t="inlineStr"/>
+      <c r="G16" s="10" t="inlineStr"/>
+      <c r="H16" s="10" t="n"/>
+      <c r="I16" s="10" t="inlineStr"/>
+      <c r="J16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>3. Люди</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Персонал</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>Проживание и питание персонала</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="D17" s="10" t="inlineStr"/>
+      <c r="E17" s="10" t="inlineStr"/>
+      <c r="F17" s="10" t="inlineStr"/>
+      <c r="G17" s="10" t="inlineStr"/>
+      <c r="H17" s="10" t="n"/>
+      <c r="I17" s="10" t="inlineStr"/>
+      <c r="J17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>3. Люди</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Персонал</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Инструктажи и обучение по требованиям площадки</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="D18" s="10" t="inlineStr"/>
+      <c r="E18" s="10" t="inlineStr"/>
+      <c r="F18" s="10" t="inlineStr"/>
+      <c r="G18" s="10" t="inlineStr"/>
+      <c r="H18" s="10" t="n"/>
+      <c r="I18" s="10" t="inlineStr"/>
+      <c r="J18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>3. Люди</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Персонал</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>Аттестации, допуски, удостоверения</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="D19" s="10" t="inlineStr"/>
+      <c r="E19" s="10" t="inlineStr"/>
+      <c r="F19" s="10" t="inlineStr"/>
+      <c r="G19" s="10" t="inlineStr"/>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="10" t="inlineStr"/>
+      <c r="J19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>3. Люди</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Персонал</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Медицинские осмотры</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="D20" s="10" t="inlineStr"/>
+      <c r="E20" s="10" t="inlineStr"/>
+      <c r="F20" s="10" t="inlineStr"/>
+      <c r="G20" s="10" t="inlineStr"/>
+      <c r="H20" s="10" t="n"/>
+      <c r="I20" s="10" t="inlineStr"/>
+      <c r="J20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>3. Люди</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Персонал</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Средства индивидуальной защиты и спецодежда</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr"/>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="D21" s="10" t="inlineStr"/>
+      <c r="E21" s="10" t="inlineStr"/>
+      <c r="F21" s="10" t="inlineStr"/>
+      <c r="G21" s="10" t="inlineStr"/>
+      <c r="H21" s="10" t="n"/>
+      <c r="I21" s="10" t="inlineStr"/>
+      <c r="J21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>3. Люди</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Персонал</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Простой по причинам, не зависящим от подрядчика</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="D22" s="10" t="inlineStr"/>
+      <c r="E22" s="10" t="inlineStr"/>
+      <c r="F22" s="10" t="inlineStr"/>
+      <c r="G22" s="10" t="inlineStr"/>
+      <c r="H22" s="10" t="n"/>
+      <c r="I22" s="10" t="inlineStr"/>
+      <c r="J22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>4. Технология и стыки</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Подготовительные работы и смежные участки</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>Подготовительные и вспомогательные операции</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr"/>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="D23" s="10" t="inlineStr"/>
+      <c r="E23" s="10" t="inlineStr"/>
+      <c r="F23" s="10" t="inlineStr"/>
+      <c r="G23" s="10" t="inlineStr"/>
+      <c r="H23" s="10" t="n"/>
+      <c r="I23" s="10" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>4. Технология и стыки</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Подготовительные работы и смежные участки</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Леса и средства подмащивания</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="D24" s="10" t="inlineStr"/>
+      <c r="E24" s="10" t="inlineStr"/>
+      <c r="F24" s="10" t="inlineStr"/>
+      <c r="G24" s="10" t="inlineStr"/>
+      <c r="H24" s="10" t="n"/>
+      <c r="I24" s="10" t="inlineStr"/>
+      <c r="J24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>4. Технология и стыки</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Подготовительные работы и смежные участки</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>Работа в стеснённых условиях и на высоте</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr"/>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="D25" s="10" t="inlineStr"/>
+      <c r="E25" s="10" t="inlineStr"/>
+      <c r="F25" s="10" t="inlineStr"/>
+      <c r="G25" s="10" t="inlineStr"/>
+      <c r="H25" s="10" t="n"/>
+      <c r="I25" s="10" t="inlineStr"/>
+      <c r="J25" s="10" t="inlineStr"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>4. Технология и стыки</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Подготовительные работы и смежные участки</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Примыкания и стыки со смежниками</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="D26" s="10" t="inlineStr"/>
+      <c r="E26" s="10" t="inlineStr"/>
+      <c r="F26" s="10" t="inlineStr"/>
+      <c r="G26" s="10" t="inlineStr"/>
+      <c r="H26" s="10" t="n"/>
+      <c r="I26" s="10" t="inlineStr"/>
+      <c r="J26" s="10" t="inlineStr"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>4. Технология и стыки</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Подготовительные работы и смежные участки</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>Восстановление повреждённого смежниками</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr"/>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="D27" s="10" t="inlineStr"/>
+      <c r="E27" s="10" t="inlineStr"/>
+      <c r="F27" s="10" t="inlineStr"/>
+      <c r="G27" s="10" t="inlineStr"/>
+      <c r="H27" s="10" t="n"/>
+      <c r="I27" s="10" t="inlineStr"/>
+      <c r="J27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>4. Технология и стыки</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Подготовительные работы и смежные участки</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Защита выполненного до сдачи</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="D28" s="10" t="inlineStr"/>
+      <c r="E28" s="10" t="inlineStr"/>
+      <c r="F28" s="10" t="inlineStr"/>
+      <c r="G28" s="10" t="inlineStr"/>
+      <c r="H28" s="10" t="n"/>
+      <c r="I28" s="10" t="inlineStr"/>
+      <c r="J28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>5. Сезон и режим</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>Работы в зимний период</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr"/>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="D29" s="10" t="inlineStr"/>
+      <c r="E29" s="10" t="inlineStr"/>
+      <c r="F29" s="10" t="inlineStr"/>
+      <c r="G29" s="10" t="inlineStr"/>
+      <c r="H29" s="10" t="n"/>
+      <c r="I29" s="10" t="inlineStr"/>
+      <c r="J29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>5. Сезон и режим</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Обогрев, тепляки, прогрев материалов</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="D30" s="10" t="inlineStr"/>
+      <c r="E30" s="10" t="inlineStr"/>
+      <c r="F30" s="10" t="inlineStr"/>
+      <c r="G30" s="10" t="inlineStr"/>
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="10" t="inlineStr"/>
+      <c r="J30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>5. Сезон и режим</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>Снегоочистка зоны работ и подходов</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr"/>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="D31" s="10" t="inlineStr"/>
+      <c r="E31" s="10" t="inlineStr"/>
+      <c r="F31" s="10" t="inlineStr"/>
+      <c r="G31" s="10" t="inlineStr"/>
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="10" t="inlineStr"/>
+      <c r="J31" s="10" t="inlineStr"/>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>5. Сезон и режим</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Ночные смены, выходные и праздники</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="D32" s="10" t="inlineStr"/>
+      <c r="E32" s="10" t="inlineStr"/>
+      <c r="F32" s="10" t="inlineStr"/>
+      <c r="G32" s="10" t="inlineStr"/>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="10" t="inlineStr"/>
+      <c r="J32" s="10" t="inlineStr"/>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>5. Сезон и режим</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>Ускорение работ по требованию второй стороны</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr"/>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="D33" s="10" t="inlineStr"/>
+      <c r="E33" s="10" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr"/>
+      <c r="G33" s="10" t="inlineStr"/>
+      <c r="H33" s="10" t="n"/>
+      <c r="I33" s="10" t="inlineStr"/>
+      <c r="J33" s="10" t="inlineStr"/>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>6. Отходы и уборка</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>Сбор мусора в зоне работ</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="D34" s="10" t="inlineStr"/>
+      <c r="E34" s="10" t="inlineStr"/>
+      <c r="F34" s="10" t="inlineStr"/>
+      <c r="G34" s="10" t="inlineStr"/>
+      <c r="H34" s="10" t="n"/>
+      <c r="I34" s="10" t="inlineStr"/>
+      <c r="J34" s="10" t="inlineStr"/>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>6. Отходы и уборка</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>Вынос мусора до места накопления</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr"/>
-      <c r="E35" s="2" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="D35" s="10" t="inlineStr"/>
+      <c r="E35" s="10" t="inlineStr"/>
+      <c r="F35" s="10" t="inlineStr"/>
+      <c r="G35" s="10" t="inlineStr"/>
+      <c r="H35" s="10" t="n"/>
+      <c r="I35" s="10" t="inlineStr"/>
+      <c r="J35" s="10" t="inlineStr"/>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>6. Отходы и уборка</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>Контейнер и вывоз</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="D36" s="10" t="inlineStr"/>
+      <c r="E36" s="10" t="inlineStr"/>
+      <c r="F36" s="10" t="inlineStr"/>
+      <c r="G36" s="10" t="inlineStr"/>
+      <c r="H36" s="10" t="n"/>
+      <c r="I36" s="10" t="inlineStr"/>
+      <c r="J36" s="10" t="inlineStr"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>6. Отходы и уборка</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>Размещение отходов и подтверждающие документы</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr"/>
-      <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="D37" s="10" t="inlineStr"/>
+      <c r="E37" s="10" t="inlineStr"/>
+      <c r="F37" s="10" t="inlineStr"/>
+      <c r="G37" s="10" t="inlineStr"/>
+      <c r="H37" s="10" t="n"/>
+      <c r="I37" s="10" t="inlineStr"/>
+      <c r="J37" s="10" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>6. Отходы и уборка</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>Ежедневная и финальная уборка</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="D38" s="10" t="inlineStr"/>
+      <c r="E38" s="10" t="inlineStr"/>
+      <c r="F38" s="10" t="inlineStr"/>
+      <c r="G38" s="10" t="inlineStr"/>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="10" t="inlineStr"/>
+      <c r="J38" s="10" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>7. Документы и приёмка</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>Ведение исполнительной документации</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr"/>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="D39" s="10" t="inlineStr"/>
+      <c r="E39" s="10" t="inlineStr"/>
+      <c r="F39" s="10" t="inlineStr"/>
+      <c r="G39" s="10" t="inlineStr"/>
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="10" t="inlineStr"/>
+      <c r="J39" s="10" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="9" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>7. Документы и приёмка</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>Геодезические работы</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="D40" s="10" t="inlineStr"/>
+      <c r="E40" s="10" t="inlineStr"/>
+      <c r="F40" s="10" t="inlineStr"/>
+      <c r="G40" s="10" t="inlineStr"/>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="10" t="inlineStr"/>
+      <c r="J40" s="10" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>7. Документы и приёмка</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>Лабораторные испытания и заключения</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr"/>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="D41" s="10" t="inlineStr"/>
+      <c r="E41" s="10" t="inlineStr"/>
+      <c r="F41" s="10" t="inlineStr"/>
+      <c r="G41" s="10" t="inlineStr"/>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="10" t="inlineStr"/>
+      <c r="J41" s="10" t="inlineStr"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="9" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>7. Документы и приёмка</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>Освидетельствование скрытых работ, повторные вызовы</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="D42" s="10" t="inlineStr"/>
+      <c r="E42" s="10" t="inlineStr"/>
+      <c r="F42" s="10" t="inlineStr"/>
+      <c r="G42" s="10" t="inlineStr"/>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="10" t="inlineStr"/>
+      <c r="J42" s="10" t="inlineStr"/>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>7. Документы и приёмка</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>Копирование, печать, передача комплектов</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="n"/>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="D43" s="10" t="inlineStr"/>
+      <c r="E43" s="10" t="inlineStr"/>
+      <c r="F43" s="10" t="inlineStr"/>
+      <c r="G43" s="10" t="inlineStr"/>
+      <c r="H43" s="10" t="n"/>
+      <c r="I43" s="10" t="inlineStr"/>
+      <c r="J43" s="10" t="inlineStr"/>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="9" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>7. Документы и приёмка</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>Участие в комиссиях и приёмке</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="n"/>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="D44" s="10" t="inlineStr"/>
+      <c r="E44" s="10" t="inlineStr"/>
+      <c r="F44" s="10" t="inlineStr"/>
+      <c r="G44" s="10" t="inlineStr"/>
+      <c r="H44" s="10" t="n"/>
+      <c r="I44" s="10" t="inlineStr"/>
+      <c r="J44" s="10" t="inlineStr"/>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>8. Деньги и обеспечение</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8. Финансирование и обеспечение</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>Услуги генподряда</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr"/>
-      <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="n"/>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="D45" s="10" t="inlineStr"/>
+      <c r="E45" s="10" t="inlineStr"/>
+      <c r="F45" s="10" t="inlineStr"/>
+      <c r="G45" s="10" t="inlineStr"/>
+      <c r="H45" s="10" t="n"/>
+      <c r="I45" s="10" t="inlineStr"/>
+      <c r="J45" s="10" t="inlineStr"/>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>8. Деньги и обеспечение</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8. Финансирование и обеспечение</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
         <is>
           <t>Гарантийное удержание</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="D46" s="10" t="inlineStr"/>
+      <c r="E46" s="10" t="inlineStr"/>
+      <c r="F46" s="10" t="inlineStr"/>
+      <c r="G46" s="10" t="inlineStr"/>
+      <c r="H46" s="10" t="n"/>
+      <c r="I46" s="10" t="inlineStr"/>
+      <c r="J46" s="10" t="inlineStr"/>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="9" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>8. Деньги и обеспечение</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8. Финансирование и обеспечение</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
         <is>
           <t>Обеспечение исполнения договора</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr"/>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="n"/>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="D47" s="10" t="inlineStr"/>
+      <c r="E47" s="10" t="inlineStr"/>
+      <c r="F47" s="10" t="inlineStr"/>
+      <c r="G47" s="10" t="inlineStr"/>
+      <c r="H47" s="10" t="n"/>
+      <c r="I47" s="10" t="inlineStr"/>
+      <c r="J47" s="10" t="inlineStr"/>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="9" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>8. Деньги и обеспечение</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8. Финансирование и обеспечение</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
         <is>
           <t>Стоимость банковской гарантии</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr"/>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="n"/>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="D48" s="10" t="inlineStr"/>
+      <c r="E48" s="10" t="inlineStr"/>
+      <c r="F48" s="10" t="inlineStr"/>
+      <c r="G48" s="10" t="inlineStr"/>
+      <c r="H48" s="10" t="n"/>
+      <c r="I48" s="10" t="inlineStr"/>
+      <c r="J48" s="10" t="inlineStr"/>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>8. Деньги и обеспечение</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8. Финансирование и обеспечение</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>Страхование</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr"/>
-      <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="n"/>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="D49" s="10" t="inlineStr"/>
+      <c r="E49" s="10" t="inlineStr"/>
+      <c r="F49" s="10" t="inlineStr"/>
+      <c r="G49" s="10" t="inlineStr"/>
+      <c r="H49" s="10" t="n"/>
+      <c r="I49" s="10" t="inlineStr"/>
+      <c r="J49" s="10" t="inlineStr"/>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>8. Деньги и обеспечение</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Отсрочка платежа: стоимость денег до оплаты</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr"/>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="n"/>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8. Финансирование и обеспечение</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Отсрочка платежа: стоимость финансирования</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr"/>
+      <c r="E50" s="10" t="inlineStr"/>
+      <c r="F50" s="10" t="inlineStr"/>
+      <c r="G50" s="10" t="inlineStr"/>
+      <c r="H50" s="10" t="n"/>
+      <c r="I50" s="10" t="inlineStr"/>
+      <c r="J50" s="10" t="inlineStr"/>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>9. Непредвиденное</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9. Непредвиденные работы и затраты</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>Резерв на непредвиденные работы</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr"/>
-      <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="n"/>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="D51" s="10" t="inlineStr"/>
+      <c r="E51" s="10" t="inlineStr"/>
+      <c r="F51" s="10" t="inlineStr"/>
+      <c r="G51" s="10" t="inlineStr"/>
+      <c r="H51" s="10" t="n"/>
+      <c r="I51" s="10" t="inlineStr"/>
+      <c r="J51" s="10" t="inlineStr"/>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="9" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>9. Непредвиденное</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9. Непредвиденные работы и затраты</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>Работы, выявленные в ходе исполнения</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="n"/>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
+      <c r="D52" s="10" t="inlineStr"/>
+      <c r="E52" s="10" t="inlineStr"/>
+      <c r="F52" s="10" t="inlineStr"/>
+      <c r="G52" s="10" t="inlineStr"/>
+      <c r="H52" s="10" t="n"/>
+      <c r="I52" s="10" t="inlineStr"/>
+      <c r="J52" s="10" t="inlineStr"/>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="C53" t="str" s="15">
+        <f>IF(COUNTBLANK(D2:D52)&gt;0,"Заполните покрытие всех 51 строк; неприменимые отметьте явно",IF(COUNTBLANK(I2:I52)&gt;0,"Заполните статус каждой строки",IF(SUMPRODUCT((I2:I52&lt;&gt;"покрыто, проверено")*(I2:I52&lt;&gt;"принято")*(I2:I52&lt;&gt;"не применяется")*(ISNUMBER(H2:H52)=FALSE))&gt;0,"Есть непокрытые затраты без числовой оценки",IF(SUMPRODUCT(((I2:I52="покрыто, проверено")+(I2:I52="принято"))*(G2:G52=""))&gt;0,"Укажите документы покрытия для закрытых позиций","Проверка заполнена; решение о цене принимает руководитель"))))</f>
+        <v>Заполните покрытие всех 51 строк; неприменимые отметьте явно</v>
+      </c>
     </row>
     <row r="54">
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>ИТОГО выпадающих затрат:</t>
-        </is>
-      </c>
-      <c r="H54" s="4">
-        <f>SUM(H2:H52)</f>
-        <v/>
+      <c r="C54" t="str" s="14">
+        <v>Предварительно не покрыто ценой:</v>
+      </c>
+      <c r="H54" t="n" s="12">
+        <f>SUMIFS(H2:H52,I2:I52,"&lt;&gt;покрыто, проверено",I2:I52,"&lt;&gt;принято",I2:I52,"&lt;&gt;не применяется")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="C55" t="inlineStr">
+      <c r="C55" t="inlineStr" s="15">
         <is>
           <t>Плановая прибыль по объекту:</t>
         </is>
       </c>
-      <c r="H55" s="5" t="n"/>
+      <c r="H55" s="11" t="n"/>
     </row>
     <row r="56">
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Доля прибыли, которую забирают выпадающие затраты:</t>
-        </is>
-      </c>
-      <c r="H56" s="6">
-        <f>IF(H55=0,"",H54/H55)</f>
-        <v/>
+      <c r="C56" t="str" s="15">
+        <v>Непокрытая сумма / плановая прибыль:</v>
+      </c>
+      <c r="H56" t="str" s="13">
+        <f>IF(OR(H55="",H55&lt;=0),"",H54/H55)</f>
       </c>
     </row>
   </sheetData>
+  <mergeCells>
+    <mergeCell ref="C53:J53"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="D2:D52" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Проверьте значение" error="Выберите значение из списка; для денежной графы введите число не меньше нуля.">
+      <formula1>"да,частично,нет,уточнить,не применяется"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="F2:F52" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Проверьте значение" error="Выберите значение из списка; для денежной графы введите число не меньше нуля.">
+      <formula1>"подрядчик,генподрядчик,заказчик,не распределено"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="I2:I52" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Проверьте значение" error="Выберите значение из списка; для денежной графы введите число не меньше нуля.">
+      <formula1>'Как заполнять'!$D$2:$D$8</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" sqref="H2:H52" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Проверьте значение" error="Выберите значение из списка; для денежной графы введите число не меньше нуля.">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" sqref="H55" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Проверьте значение" error="Выберите значение из списка; для денежной графы введите число не меньше нуля.">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="8" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1673,7 +1812,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1683,114 +1822,121 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Графа</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>Что вписать</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Порядок заполнения</t>
+        </is>
+      </c>
+      <c r="D1" t="str">
+        <v>Статусы реестра</v>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Учтено в смете</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>«да» — есть отдельная позиция сметы; «частично» — позиция есть, но покрывает не весь объём затраты; «нет» — отдельной позиции нет; «не знаю» — вопрос в запрос второй стороне. «Не знаю» — законный ответ на этом этапе, пустая клетка — нет.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="B2" t="str" s="18">
+        <v>Укажите «да», «частично», «нет», «уточнить» или «не применяется». Проверяйте покрытие расценкой, ресурсом и начислениями. Все 51 строки требуют отметки.</v>
+      </c>
+      <c r="D2" t="str">
+        <v>проверить</v>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>Позиция сметы №</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Номер строки сметы для значений «да» и «частично». Пусто для остальных.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Чья зона</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>«подрядчик», «генподрядчик», «заказчик» или «в договоре не распределено». Последнее — рабочий результат: именно эти строки идут в запрос первыми.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="B3" t="str" s="18">
+        <v>Номер позиции или раздела расчёта, которым расход покрыт полностью либо частично. При отсутствии покрытия оставьте пустым.</v>
+      </c>
+      <c r="D3" t="str">
+        <v>в запросе</v>
+      </c>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ответственная сторона</t>
+        </is>
+      </c>
+      <c r="B4" t="str" s="18">
+        <v>Укажите подрядчика, генподрядчика, заказчика либо «не распределено»; сошлитесь на договор, проект или письменное решение.</v>
+      </c>
+      <c r="D4" t="str">
+        <v>в протоколе разногласий</v>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Чем подтверждено</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Документ, из которого видно, чья это зона: пункт договора, регламент площадки, письмо, лист проекта. Ссылка на устную договорённость подтверждением не является.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Оценка, ₽</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Ваша оценка затраты на весь объём работ по договору. Точность на этом этапе не нужна — нужен порядок величины, чтобы увидеть общую сумму.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="B5" t="str" s="18">
+        <v>Реквизиты документа и пункта о распределении расхода или его покрытии. Для «покрыто, проверено» и «принято» документ обязателен.</v>
+      </c>
+      <c r="D5" t="str">
+        <v>покрыто, проверено</v>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" t="str" s="17">
+        <v>Непокрытая часть, ₽</v>
+      </c>
+      <c r="B6" t="str" s="18">
+        <v>Введите только оценку непокрытой части расхода на весь объём работ. Ноль означает проверенное отсутствие остатка. Пустая клетка — оценка отсутствует.</v>
+      </c>
+      <c r="D6" t="str">
+        <v>принято</v>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>«покрыто, проверено» — снята после проверки накладных расходов; «в запросе» — включена в письмо второй стороне; «в протоколе разногласий»; «принято» — включена в смету; «снято» — отказались и вы согласились нести затрату.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="B7" t="str" s="18">
+        <v>«проверить», «в запросе», «в протоколе разногласий», «риск принят» входят в предварительный итог. «покрыто, проверено», «принято», «не применяется» исключаются из него. «Риск принят» означает, что компания согласилась нести непокрытый расход.</v>
+      </c>
+      <c r="D7" t="str">
+        <v>не применяется</v>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>ИТОГО и доля прибыли</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Считаются формулами. Доля прибыли — то число, по которому принимается решение о подписании; заполните строку «Плановая прибыль по объекту», чтобы она посчиталась.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="B8" t="str" s="18">
+        <v>H54 суммирует непокрытую часть с учётом статуса. H55 — плановая прибыль компании по объекту до этих расходов. H56 показывает долю прибыли при положительном H55. Проверяйте сообщение над итогом и незаполненные оценки.</v>
+      </c>
+      <c r="D8" t="str">
+        <v>риск принят</v>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Порядок работы</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Реестр заполняется до подписания договора и живёт до его подписания. После подписания он остаётся доказательством того, что вопрос был поставлен письменно и когда именно.</t>
-        </is>
+      <c r="B9" t="str" s="18">
+        <v>Для новой затраты используйте подходящую строку с расшифровкой в комментарии и без повторного счёта. Формулы охватывают строки 2–52. Строки ниже итогов в расчёт не входят. До подписания подтвердите полноту проверки и согласуйте остаток риска.</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>